--- a/output/2026-09-13_21_Croazia_Primorsko-goranska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_21_Croazia_Primorsko-goranska_Impiantistica_aspirazione_industriale.xlsx
@@ -498,10 +498,9 @@
           <t>+385 51 818 626</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Produzione e installazione impianti di ventilazione industriale e otprasivanje (captazione polveri): filtri, cicloni, sili, ventilatori di trasporto, elementi di ventilazione, cabine insonorizzate, carpenteria metallica. ISO 9001:2000. Confermato tramite piu fonti indipendenti (tvrtke.hr, croatiayp.com, ekvarner.info).</t>
+          <t>Produzione e installazione impianti di ventilazione industriale e otprasivanje (captazione polveri): filtri, cicloni, sili, ventilatori di trasporto, elementi di ventilazione, cabine insonorizzate, carpenteria metallica. ISO 9001:2000. Confermato tramite piu fonti indipendenti (tvrtke.hr, croatiayp.com, ekvarner.info). [DUPLICATO — vedi anche: 2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">

--- a/output/2026-09-13_21_Croazia_Primorsko-goranska_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_21_Croazia_Primorsko-goranska_Impiantistica_aspirazione_industriale.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
